--- a/excel/hmd_2d.xlsx
+++ b/excel/hmd_2d.xlsx
@@ -8,19 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamilton\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D115D9-2D9A-43E6-A8B2-242D4A47FF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B1B001-4F90-4E6F-96F9-46DB2304ED63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9330" yWindow="2205" windowWidth="18285" windowHeight="12375" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="2820" windowWidth="18285" windowHeight="12375" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="非均布_Tri3_4-32" sheetId="1" r:id="rId1"/>
+    <sheet name="非均布_Tri6_4-32" sheetId="2" r:id="rId2"/>
+    <sheet name="均布_Tri3_4-32" sheetId="3" r:id="rId3"/>
+    <sheet name="均布_Tri6_4-32" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -346,39 +350,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A2:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" dyDescent="0.2">
       <c r="A2">
-        <v>0.0</v>
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.64799394160628643</v>
       </c>
       <c r="C2">
-        <v>-0.4810084554209248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>0.25313615006197671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
+      <c r="B3">
+        <v>0.36261286421463995</v>
+      </c>
       <c r="C3">
-        <v>-0.5677662061792664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-0.32796450042747255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
+      <c r="B4">
+        <v>0.86130729585426413</v>
+      </c>
       <c r="C4">
-        <v>-1.390931968253061</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>-0.17894502810715426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" dyDescent="0.2">
       <c r="A5">
-        <v>-0.9030899869919435</v>
+        <v>-0.90308998699194354</v>
+      </c>
+      <c r="B5">
+        <v>0.58058931112635381</v>
       </c>
       <c r="C5">
-        <v>-0.5310860175963289</v>
+        <v>-0.75327134425965181</v>
       </c>
     </row>
   </sheetData>
@@ -394,39 +410,51 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE83A220-CD61-4BB3-BCF7-83B7562F73A3}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A2:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" dyDescent="0.2">
       <c r="A2">
-        <v>0.0</v>
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.44023351011400469</v>
       </c>
       <c r="C2">
-        <v>-0.15887336010035175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>-0.25749423978618147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
+      <c r="B3">
+        <v>0.20320795323058088</v>
+      </c>
       <c r="C3">
-        <v>0.22574281491066495</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-0.78621055311583987</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
+      <c r="B4">
+        <v>0.2318284394591523</v>
+      </c>
       <c r="C4">
-        <v>-0.14560234531851107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>-1.130574260673932</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" dyDescent="0.2">
       <c r="A5">
-        <v>-0.9030899869919435</v>
+        <v>-0.90308998699194354</v>
+      </c>
+      <c r="B5">
+        <v>-5.018907047874871E-2</v>
       </c>
       <c r="C5">
-        <v>-0.14728359025112092</v>
+        <v>-1.6836831213973706</v>
       </c>
     </row>
   </sheetData>
@@ -441,6 +469,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2E2034-4C97-494A-856C-B015D42B780A}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>0.0</v>
+      </c>
+      <c r="B2">
+        <v>-0.10124301727860854</v>
+      </c>
+      <c r="C2">
+        <v>-0.5856099674864046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>-0.3010299956639812</v>
+      </c>
+      <c r="B3">
+        <v>0.0717402800733706</v>
+      </c>
+      <c r="C3">
+        <v>-0.7206812659972617</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>-0.6020599913279624</v>
+      </c>
+      <c r="B4">
+        <v>-0.27750922347898344</v>
+      </c>
+      <c r="C4">
+        <v>-1.3598571456456392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>-0.9030899869919435</v>
+      </c>
+      <c r="B5">
+        <v>-0.5812737632323239</v>
+      </c>
+      <c r="C5">
+        <v>-1.9595858121933882</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>-1.2041199826559248</v>
+      </c>
+      <c r="B6">
+        <v>-0.8806960065713183</v>
+      </c>
+      <c r="C6">
+        <v>-2.5580386454263717</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81738D9B-CEB0-41EE-BCB7-2D6251DFBC30}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -448,32 +543,44 @@
       <c r="A2">
         <v>0.0</v>
       </c>
+      <c r="B2">
+        <v>-0.04781801574421997</v>
+      </c>
       <c r="C2">
-        <v>0.3327004020509138</v>
+        <v>-0.8776085689273113</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
+      <c r="B3">
+        <v>-0.3979081829920863</v>
+      </c>
       <c r="C3">
-        <v>0.31910959494994984</v>
+        <v>-1.4548610041418053</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
+      <c r="B4">
+        <v>-0.7822891010657717</v>
+      </c>
       <c r="C4">
-        <v>0.31956404078451517</v>
+        <v>-2.158428369492489</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <v>-0.9030899869919435</v>
       </c>
+      <c r="B5">
+        <v>-1.1389315230058117</v>
+      </c>
       <c r="C5">
-        <v>0.3245609533959728</v>
+        <v>-2.8406576392013685</v>
       </c>
     </row>
   </sheetData>
